--- a/translation/EntityTranslate.xlsx
+++ b/translation/EntityTranslate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Documents/Projekte/FYAYC_intern/gitHub/translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9F2017-93BB-CF43-AC85-BDBC122AB300}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C5C406-A1CF-B646-A0BF-F5E872019E72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="27960" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="24800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Search Results Details" sheetId="1" r:id="rId1"/>
@@ -517,13 +517,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:F36DA4B9-5637-6234-ABA8-4D2DC391EB38;
-Class:oracle.dbtools.crest.model.design.logical.Entity</t>
+          <t xml:space="preserve">ObjectID:F36DA4B9-5637-6234-ABA8-4D2DC391EB38;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Entity</t>
         </r>
       </text>
     </comment>
@@ -787,13 +795,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:0035B365-CE5D-205A-0B0E-54ECA27EEECE;
-Class:oracle.dbtools.crest.model.design.logical.Entity</t>
+          <t xml:space="preserve">ObjectID:0035B365-CE5D-205A-0B0E-54ECA27EEECE;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Entity</t>
         </r>
       </text>
     </comment>
@@ -892,13 +908,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:042A86B2-01B0-2BF0-D0D9-801BD9612C6B;
-Class:oracle.dbtools.crest.model.design.logical.Entity</t>
+          <t xml:space="preserve">ObjectID:042A86B2-01B0-2BF0-D0D9-801BD9612C6B;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Entity</t>
         </r>
       </text>
     </comment>
@@ -952,13 +976,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:4E117E57-CFB5-EF2C-4F8F-638438B13812;
-Class:oracle.dbtools.crest.model.design.logical.Entity</t>
+          <t xml:space="preserve">ObjectID:4E117E57-CFB5-EF2C-4F8F-638438B13812;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Entity</t>
         </r>
       </text>
     </comment>
@@ -1597,7 +1629,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="740">
   <si>
     <t>EntityTranslate</t>
   </si>
@@ -3259,40 +3291,13 @@
     <t>A1-A4</t>
   </si>
   <si>
-    <t>*DE* Administrativebene</t>
-  </si>
-  <si>
-    <t>*DE* A1-A4</t>
-  </si>
-  <si>
     <t>Postalisch-geographische Lokalisation
 Jede Adresse ist für einen Akteur definiert. D.h. die selbe Adresse kann mehrfach vorkommen.
 Falls ein generelles Adressverzeichnis als Referenz geführt wird (Basisadresse), muss das zusätlich erfasst werden.
 Dann wird diese Entität zur Verknüpfung zwischen Akteur und Basisadresse.</t>
   </si>
   <si>
-    <t>*DE* Postalisch-geographische Lokalisation  Jede Adresse ist für einen Akteur definiert. D.h. die selbe Adresse kann mehrfach vorkommen. Falls ein generelles Adressverzeichnis als Referenz geführt wird (Basisadresse), muss das zusätlich erfasst werden. Dann wird diese Entität zur Verknüpfung zwischen Akteur und Basisadresse.</t>
-  </si>
-  <si>
-    <t>*DE* Adresse</t>
-  </si>
-  <si>
     <t>Zweck der Adresse (Finanz, Post, Lieferung etc.)</t>
-  </si>
-  <si>
-    <t>*DE* Adresstyp</t>
-  </si>
-  <si>
-    <t>*DE* Gebäudename</t>
-  </si>
-  <si>
-    <t>*DE* Geokoordinate</t>
-  </si>
-  <si>
-    <t>*DE* Hausnr</t>
-  </si>
-  <si>
-    <t>*DE* Strassenname</t>
   </si>
   <si>
     <t>*DE* Zweck der Adresse (Finanz, Post, Lieferung etc.)</t>
@@ -3375,9 +3380,6 @@
   </si>
   <si>
     <t>*DE* Finanzierungspartner</t>
-  </si>
-  <si>
-    <t>*DE* Gebiet</t>
   </si>
   <si>
     <t>Lokale Variante einer Sprache
@@ -3415,13 +3417,7 @@
     <t>*DE* Ein geographisches Gebilde das nach geographischen, polititischen oder postalischen Kriterien in dieser Form definiert ist.</t>
   </si>
   <si>
-    <t>*DE* Geografische Einheit</t>
-  </si>
-  <si>
     <t>Fläche eines Gebiets als geo-Information</t>
-  </si>
-  <si>
-    <t>*DE* GeoInformation</t>
   </si>
   <si>
     <t>*DE* Fläche eines Gebiets als geo-Information</t>
@@ -3533,21 +3529,6 @@
     <t xml:space="preserve">*DE* Kommunikationskanäle und ihre Adresse </t>
   </si>
   <si>
-    <t>*DE* Kommunikationsmittel</t>
-  </si>
-  <si>
-    <t>*DE* Fixnet Tel Nr</t>
-  </si>
-  <si>
-    <t>*DE* Mobil Tel Nr</t>
-  </si>
-  <si>
-    <t>*DE* Webseite</t>
-  </si>
-  <si>
-    <t>*DE* eMail</t>
-  </si>
-  <si>
     <t>Informationen über Markteilnehmer Partner (Kunden, Lieferanten, Wettberwerber)</t>
   </si>
   <si>
@@ -3573,21 +3554,6 @@
   </si>
   <si>
     <t xml:space="preserve">*DE* Land gemäss ISO-Liste ISO-3166-1  Gemäss NUTS (https://de.wikipedia.org/wiki/NUTS) ist das Land die Gebietsstufe NUTS 0 </t>
-  </si>
-  <si>
-    <t>*DE* Land</t>
-  </si>
-  <si>
-    <t>*DE* ISO2_Code</t>
-  </si>
-  <si>
-    <t>*DE* ISO3_Code</t>
-  </si>
-  <si>
-    <t>*DE* ISO_Code_numerisch</t>
-  </si>
-  <si>
-    <t>*DE* TopLevelDomain</t>
   </si>
   <si>
     <t>Geschäftsfähige Einheit die einen Leasingvertrag für Produkt abgeschlossen hat.
@@ -3681,12 +3647,6 @@
     <t>P1-P3</t>
   </si>
   <si>
-    <t>*DE* PLZ-Ebene</t>
-  </si>
-  <si>
-    <t>*DE* Postleitzahl</t>
-  </si>
-  <si>
     <t>*DE* P1-P3</t>
   </si>
   <si>
@@ -3927,12 +3887,63 @@
   <si>
     <t>ZIP area</t>
   </si>
+  <si>
+    <t>administrative level</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Postal geographical localization Each address is defined for one actor. This means that the same address can occur more than once. If a general address directory is maintained as a reference (base address), this must be entered additionally. Then this entity becomes the link between actor and base address.</t>
+  </si>
+  <si>
+    <t>Building name</t>
+  </si>
+  <si>
+    <t>Type of address</t>
+  </si>
+  <si>
+    <t>Geographical coordinate</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Streetname</t>
+  </si>
+  <si>
+    <t>zip level</t>
+  </si>
+  <si>
+    <t>zip code</t>
+  </si>
+  <si>
+    <t>communication medium</t>
+  </si>
+  <si>
+    <t>TelNo fix</t>
+  </si>
+  <si>
+    <t>TelNo mobile</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>Geographical Unit</t>
+  </si>
+  <si>
+    <t>ISO_Code_numeric</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3958,6 +3969,12 @@
       <i/>
       <sz val="10"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4396,7 +4413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="396" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="304" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -4416,13 +4433,13 @@
         <v>542</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>741</v>
+        <v>717</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>742</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4464,10 +4481,10 @@
         <v>547</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>548</v>
+        <v>723</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4507,10 +4524,10 @@
         <v>542</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>19</v>
@@ -4519,10 +4536,10 @@
         <v>542</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>551</v>
+        <v>725</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>552</v>
+        <v>724</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>542</v>
@@ -4558,19 +4575,19 @@
         <v>209</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>209</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>554</v>
+        <v>727</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4587,7 +4604,7 @@
         <v>542</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>555</v>
+        <v>726</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>542</v>
@@ -4607,7 +4624,7 @@
         <v>542</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>556</v>
+        <v>728</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>542</v>
@@ -4627,7 +4644,7 @@
         <v>542</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>557</v>
+        <v>729</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>542</v>
@@ -4647,7 +4664,7 @@
         <v>542</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>558</v>
+        <v>730</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>542</v>
@@ -4690,10 +4707,10 @@
         <v>542</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>21</v>
@@ -4702,10 +4719,10 @@
         <v>542</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>542</v>
@@ -4748,10 +4765,10 @@
         <v>542</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>23</v>
@@ -4760,10 +4777,10 @@
         <v>542</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>542</v>
@@ -4803,28 +4820,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4866,7 +4883,7 @@
         <v>542</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>542</v>
@@ -4909,10 +4926,10 @@
         <v>542</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>27</v>
@@ -4921,10 +4938,10 @@
         <v>542</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>542</v>
@@ -4967,10 +4984,10 @@
         <v>542</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>65</v>
@@ -4979,10 +4996,10 @@
         <v>542</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>542</v>
@@ -5025,10 +5042,10 @@
         <v>542</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>67</v>
@@ -5037,10 +5054,10 @@
         <v>542</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>542</v>
@@ -5083,10 +5100,10 @@
         <v>542</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>69</v>
@@ -5095,10 +5112,10 @@
         <v>542</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>542</v>
@@ -5156,7 +5173,7 @@
         <v>545</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>584</v>
+        <v>739</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>542</v>
@@ -5199,10 +5216,10 @@
         <v>542</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>73</v>
@@ -5211,10 +5228,10 @@
         <v>542</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>542</v>
@@ -5250,19 +5267,19 @@
         <v>243</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>243</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5279,7 +5296,7 @@
         <v>542</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>542</v>
@@ -5322,10 +5339,10 @@
         <v>542</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>75</v>
@@ -5334,10 +5351,10 @@
         <v>542</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>594</v>
+        <v>737</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>542</v>
@@ -5373,19 +5390,19 @@
         <v>222</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>222</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>596</v>
+        <v>222</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5402,7 +5419,7 @@
         <v>542</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>590</v>
+        <v>250</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>542</v>
@@ -5445,10 +5462,10 @@
         <v>542</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>77</v>
@@ -5457,10 +5474,10 @@
         <v>542</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>542</v>
@@ -5505,7 +5522,7 @@
         <v>542</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>542</v>
@@ -5548,10 +5565,10 @@
         <v>542</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>79</v>
@@ -5560,10 +5577,10 @@
         <v>542</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>542</v>
@@ -5599,19 +5616,19 @@
         <v>257</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>257</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5651,10 +5668,10 @@
         <v>542</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>83</v>
@@ -5663,10 +5680,10 @@
         <v>542</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>542</v>
@@ -5709,10 +5726,10 @@
         <v>542</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>81</v>
@@ -5721,10 +5738,10 @@
         <v>542</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>542</v>
@@ -5767,10 +5784,10 @@
         <v>542</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>85</v>
@@ -5779,10 +5796,10 @@
         <v>542</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>542</v>
@@ -5825,10 +5842,10 @@
         <v>542</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>87</v>
@@ -5837,10 +5854,10 @@
         <v>542</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>542</v>
@@ -5898,7 +5915,7 @@
         <v>542</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>542</v>
@@ -5941,10 +5958,10 @@
         <v>542</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>91</v>
@@ -5953,10 +5970,10 @@
         <v>542</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>542</v>
@@ -6001,7 +6018,7 @@
         <v>542</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>542</v>
@@ -6012,19 +6029,19 @@
         <v>269</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>269</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6064,10 +6081,10 @@
         <v>542</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>95</v>
@@ -6076,10 +6093,10 @@
         <v>542</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>630</v>
+        <v>733</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>542</v>
@@ -6124,7 +6141,7 @@
         <v>542</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>631</v>
+        <v>734</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>542</v>
@@ -6144,7 +6161,7 @@
         <v>542</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>632</v>
+        <v>735</v>
       </c>
       <c r="G97" s="5" t="s">
         <v>542</v>
@@ -6164,7 +6181,7 @@
         <v>542</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>633</v>
+        <v>736</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>542</v>
@@ -6184,7 +6201,7 @@
         <v>542</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>634</v>
+        <v>214</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>542</v>
@@ -6227,10 +6244,10 @@
         <v>542</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>97</v>
@@ -6239,10 +6256,10 @@
         <v>542</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>542</v>
@@ -6285,10 +6302,10 @@
         <v>542</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>93</v>
@@ -6297,10 +6314,10 @@
         <v>542</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>542</v>
@@ -6343,10 +6360,10 @@
         <v>542</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>99</v>
@@ -6355,10 +6372,10 @@
         <v>542</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>643</v>
+        <v>99</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>542</v>
@@ -6403,7 +6420,7 @@
         <v>542</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>644</v>
+        <v>235</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>542</v>
@@ -6423,7 +6440,7 @@
         <v>542</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>645</v>
+        <v>239</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>542</v>
@@ -6443,7 +6460,7 @@
         <v>542</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>646</v>
+        <v>738</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>542</v>
@@ -6463,7 +6480,7 @@
         <v>542</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>647</v>
+        <v>265</v>
       </c>
       <c r="G113" s="5" t="s">
         <v>542</v>
@@ -6506,10 +6523,10 @@
         <v>542</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>103</v>
@@ -6518,10 +6535,10 @@
         <v>542</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>542</v>
@@ -6564,10 +6581,10 @@
         <v>542</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>101</v>
@@ -6576,10 +6593,10 @@
         <v>542</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>542</v>
@@ -6615,19 +6632,19 @@
         <v>267</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>267</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6644,10 +6661,10 @@
         <v>542</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>656</v>
+        <v>634</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>658</v>
+        <v>636</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6687,10 +6704,10 @@
         <v>542</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>105</v>
@@ -6699,10 +6716,10 @@
         <v>542</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>542</v>
@@ -6745,10 +6762,10 @@
         <v>542</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>662</v>
+        <v>640</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>662</v>
+        <v>640</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>109</v>
@@ -6757,10 +6774,10 @@
         <v>542</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>664</v>
+        <v>642</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>542</v>
@@ -6803,10 +6820,10 @@
         <v>542</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>111</v>
@@ -6815,10 +6832,10 @@
         <v>542</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>542</v>
@@ -6863,7 +6880,7 @@
         <v>542</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>542</v>
@@ -6903,25 +6920,25 @@
         <v>117</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>117</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>744</v>
+        <v>720</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>542</v>
@@ -6957,19 +6974,19 @@
         <v>254</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>254</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>670</v>
+        <v>731</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>672</v>
+        <v>648</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6986,7 +7003,7 @@
         <v>542</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>671</v>
+        <v>732</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>542</v>
@@ -7029,10 +7046,10 @@
         <v>542</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>113</v>
@@ -7041,10 +7058,10 @@
         <v>542</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>542</v>
@@ -7087,10 +7104,10 @@
         <v>542</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>115</v>
@@ -7099,10 +7116,10 @@
         <v>542</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>542</v>
@@ -7147,7 +7164,7 @@
         <v>542</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>677</v>
+        <v>653</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>542</v>
@@ -7167,7 +7184,7 @@
         <v>542</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>542</v>
@@ -7210,10 +7227,10 @@
         <v>542</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>119</v>
@@ -7222,10 +7239,10 @@
         <v>542</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>542</v>
@@ -7268,10 +7285,10 @@
         <v>542</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>121</v>
@@ -7280,10 +7297,10 @@
         <v>542</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="I157" s="4" t="s">
         <v>542</v>
@@ -7326,10 +7343,10 @@
         <v>542</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>123</v>
@@ -7338,10 +7355,10 @@
         <v>542</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="I159" s="4" t="s">
         <v>542</v>
@@ -7386,7 +7403,7 @@
         <v>542</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>542</v>
@@ -7429,10 +7446,10 @@
         <v>542</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>125</v>
@@ -7441,10 +7458,10 @@
         <v>542</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>542</v>
@@ -7487,10 +7504,10 @@
         <v>542</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>127</v>
@@ -7499,10 +7516,10 @@
         <v>542</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>693</v>
+        <v>669</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>694</v>
+        <v>670</v>
       </c>
       <c r="I168" s="4" t="s">
         <v>542</v>
@@ -7542,28 +7559,28 @@
         <v>129</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>695</v>
+        <v>671</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>696</v>
+        <v>672</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>696</v>
+        <v>672</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>129</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>695</v>
+        <v>671</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>697</v>
+        <v>673</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>698</v>
+        <v>674</v>
       </c>
       <c r="I170" s="4" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -7605,7 +7622,7 @@
         <v>542</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>542</v>
@@ -7625,7 +7642,7 @@
         <v>542</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>701</v>
+        <v>677</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>542</v>
@@ -7645,7 +7662,7 @@
         <v>542</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>542</v>
@@ -7688,10 +7705,10 @@
         <v>542</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>702</v>
+        <v>678</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>702</v>
+        <v>678</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>131</v>
@@ -7700,10 +7717,10 @@
         <v>542</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>703</v>
+        <v>679</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>704</v>
+        <v>680</v>
       </c>
       <c r="I179" s="4" t="s">
         <v>542</v>
@@ -7748,7 +7765,7 @@
         <v>542</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>542</v>
@@ -7791,10 +7808,10 @@
         <v>542</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>705</v>
+        <v>681</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>705</v>
+        <v>681</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>135</v>
@@ -7803,10 +7820,10 @@
         <v>542</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>707</v>
+        <v>683</v>
       </c>
       <c r="I186" s="4" t="s">
         <v>542</v>
@@ -7849,10 +7866,10 @@
         <v>542</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>708</v>
+        <v>684</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>708</v>
+        <v>684</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>137</v>
@@ -7861,10 +7878,10 @@
         <v>542</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>709</v>
+        <v>685</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>710</v>
+        <v>686</v>
       </c>
       <c r="I188" s="4" t="s">
         <v>542</v>
@@ -7907,10 +7924,10 @@
         <v>542</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>711</v>
+        <v>687</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>711</v>
+        <v>687</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>139</v>
@@ -7919,10 +7936,10 @@
         <v>542</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>712</v>
+        <v>688</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>713</v>
+        <v>689</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>542</v>
@@ -7965,10 +7982,10 @@
         <v>542</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>141</v>
@@ -7977,10 +7994,10 @@
         <v>542</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>715</v>
+        <v>691</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>542</v>
@@ -8038,7 +8055,7 @@
         <v>542</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>717</v>
+        <v>693</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>542</v>
@@ -8096,7 +8113,7 @@
         <v>542</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="I196" s="4" t="s">
         <v>542</v>
@@ -8154,7 +8171,7 @@
         <v>542</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>719</v>
+        <v>695</v>
       </c>
       <c r="I198" s="4" t="s">
         <v>542</v>
@@ -8212,7 +8229,7 @@
         <v>542</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>720</v>
+        <v>696</v>
       </c>
       <c r="I200" s="4" t="s">
         <v>542</v>
@@ -8270,7 +8287,7 @@
         <v>542</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>721</v>
+        <v>697</v>
       </c>
       <c r="I202" s="4" t="s">
         <v>542</v>
@@ -8328,7 +8345,7 @@
         <v>542</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="I204" s="4" t="s">
         <v>542</v>
@@ -8386,7 +8403,7 @@
         <v>542</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>723</v>
+        <v>699</v>
       </c>
       <c r="I206" s="4" t="s">
         <v>542</v>
@@ -8444,7 +8461,7 @@
         <v>542</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>724</v>
+        <v>700</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>542</v>
@@ -8502,7 +8519,7 @@
         <v>542</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>725</v>
+        <v>701</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>542</v>
@@ -8560,7 +8577,7 @@
         <v>542</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>726</v>
+        <v>702</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>542</v>
@@ -8618,7 +8635,7 @@
         <v>542</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>727</v>
+        <v>703</v>
       </c>
       <c r="I214" s="4" t="s">
         <v>542</v>
@@ -8676,7 +8693,7 @@
         <v>542</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>728</v>
+        <v>704</v>
       </c>
       <c r="I216" s="4" t="s">
         <v>542</v>
@@ -8734,7 +8751,7 @@
         <v>542</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>729</v>
+        <v>705</v>
       </c>
       <c r="I218" s="4" t="s">
         <v>542</v>
@@ -8792,7 +8809,7 @@
         <v>542</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>730</v>
+        <v>706</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>542</v>
@@ -8850,7 +8867,7 @@
         <v>542</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>542</v>
@@ -8908,7 +8925,7 @@
         <v>542</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="I224" s="4" t="s">
         <v>542</v>
@@ -8966,7 +8983,7 @@
         <v>542</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>733</v>
+        <v>709</v>
       </c>
       <c r="I226" s="4" t="s">
         <v>542</v>
@@ -9024,7 +9041,7 @@
         <v>542</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>734</v>
+        <v>710</v>
       </c>
       <c r="I228" s="4" t="s">
         <v>542</v>
@@ -9082,7 +9099,7 @@
         <v>542</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>735</v>
+        <v>711</v>
       </c>
       <c r="I230" s="4" t="s">
         <v>542</v>
@@ -9127,7 +9144,7 @@
         <v>542</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>542</v>
@@ -9147,7 +9164,7 @@
         <v>542</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>737</v>
+        <v>713</v>
       </c>
       <c r="G235" s="5" t="s">
         <v>542</v>
@@ -9167,7 +9184,7 @@
         <v>542</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="G236" s="5" t="s">
         <v>542</v>
@@ -9225,7 +9242,7 @@
         <v>542</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="I239" s="4" t="s">
         <v>542</v>
@@ -9270,14 +9287,13 @@
         <v>263</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>

--- a/translation/EntityTranslate.xlsx
+++ b/translation/EntityTranslate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Documents/Projekte/FYAYC_intern/gitHub/translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C5C406-A1CF-B646-A0BF-F5E872019E72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F8A1C1-A61A-DC46-8335-6804B38DF3D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="24800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,13 +67,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:80D2A6F4-56D6-88E4-2E84-676699D4EBF2;
-Class:oracle.dbtools.crest.model.design.logical.Entity</t>
+          <t xml:space="preserve">ObjectID:80D2A6F4-56D6-88E4-2E84-676699D4EBF2;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Entity</t>
         </r>
       </text>
     </comment>
@@ -82,13 +90,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:E285B361-7F82-B5D1-44DC-064EFA1C70D3;
-Class:oracle.dbtools.crest.model.design.logical.Attribute</t>
+          <t xml:space="preserve">ObjectID:E285B361-7F82-B5D1-44DC-064EFA1C70D3;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Attribute</t>
         </r>
       </text>
     </comment>
@@ -112,13 +128,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:FF67251E-70A4-8810-9AAE-8D3085C3FC14;
-Class:oracle.dbtools.crest.model.design.logical.Attribute</t>
+          <t xml:space="preserve">ObjectID:FF67251E-70A4-8810-9AAE-8D3085C3FC14;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Attribute</t>
         </r>
       </text>
     </comment>
@@ -1629,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="737">
   <si>
     <t>EntityTranslate</t>
   </si>
@@ -3282,9 +3306,6 @@
 Flurnamen, Gemeindegebiete, alte Gemeindenamen (unterteilen Gemeinde) oder weitere Stufen</t>
   </si>
   <si>
-    <t>*DE* Gebietsunterteilung eines Landes in kleinere Einheiten.  Gemäss NUTS (https://de.wikipedia.org/wiki/NUTS) ist das Land die Gebietsstufe NUTS 0 NUTS 0 Nationalstaat NUTS 1 “major socio-economic regions (grouping basic regions)” … größere Regionen/Landesteile NUTS 2  “basic regions (for the application of regional policies)” … mittelgroße Regionen, Millionenstädte NUTS 3 “small regions (for specific diagnoses)” … kleinere Regionen, teils schon Großstädte LAU 1 o.A. … kommunale Verwaltungsverbände, teils Gemeinden (nicht in allen Staaten definiert) LAU 2 “municipalities or equivalent units” … Gemeinden, teils Gemeindegliederungen  Es kann weitere Hierarchiestufenbezeichnungen geben: Deutschland A0: Land A1: Bundesland A2: leer A3: Landkreis A4: leer A5: Gemeinde: Administrative Gemeinde im jeweiligen Land Flurnamen, Gemeindegebiete, alte Gemeindenamen (unterteilen Gemeinde) oder weitere Stufen</t>
-  </si>
-  <si>
     <t>Attributes</t>
   </si>
   <si>
@@ -3300,26 +3321,11 @@
     <t>Zweck der Adresse (Finanz, Post, Lieferung etc.)</t>
   </si>
   <si>
-    <t>*DE* Zweck der Adresse (Finanz, Post, Lieferung etc.)</t>
-  </si>
-  <si>
     <t>Person oder Firma, die für uns (in einem Gebiet) die Vermittlung von Geschäften übernimmt.
 Handelt in dieser Rolle selber nicht mit den Waren. Hat also weder Lager noch ist sie Adressat von Lieferungen.</t>
   </si>
   <si>
-    <t>*DE* Person oder Firma, die für uns (in einem Gebiet) die Vermittlung von Geschäften übernimmt. Handelt in dieser Rolle selber nicht mit den Waren. Hat also weder Lager noch ist sie Adressat von Lieferungen.</t>
-  </si>
-  <si>
-    <t>*DE* Agent</t>
-  </si>
-  <si>
     <t>Stamminformationen, die über ein Unternehmen hinaus Gültigkeit haben bzw. durch Standards vorgegeben sind.</t>
-  </si>
-  <si>
-    <t>*DE* Stamminformationen, die über ein Unternehmen hinaus Gültigkeit haben bzw. durch Standards vorgegeben sind.</t>
-  </si>
-  <si>
-    <t>*DE* Allg. Information</t>
   </si>
   <si>
     <t>Kontaktperson</t>
@@ -3331,34 +3337,10 @@
 Synonym von Ansprechpartner nach Kontaktperson geändert</t>
   </si>
   <si>
-    <t>*DE* Funktion einer Person für eine juristische Einheit. Im Spezialfall kann eine Person als Einzelfirma ihr eigener Ansprechspartner sein.  26.6.18 - THU: Namen von Kontaktperson nach Ansprechpartner geändert Synonym von Ansprechpartner nach Kontaktperson geändert</t>
-  </si>
-  <si>
-    <t>*DE* Ansprechpartner</t>
-  </si>
-  <si>
-    <t>*DE* Kontaktperson</t>
-  </si>
-  <si>
-    <t>*DE* Gültigkeitsperiode</t>
-  </si>
-  <si>
     <t>Person oder Firma, die eine Maschine in seinem physischen Besitz hat.</t>
   </si>
   <si>
-    <t>*DE* Person oder Firma, die eine Maschine in seinem physischen Besitz hat.</t>
-  </si>
-  <si>
-    <t>*DE* Besitzer</t>
-  </si>
-  <si>
     <t>Person, Organisation die Maschinenexemplare rechtlich besitzt.</t>
-  </si>
-  <si>
-    <t>*DE* Person, Organisation die Maschinenexemplare rechtlich besitzt.</t>
-  </si>
-  <si>
-    <t>*DE* Eigentümer</t>
   </si>
   <si>
     <t xml:space="preserve">B2C Handelseinheit
@@ -3366,20 +3348,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* B2C Handelseinheit Geschäft, Lokal, Filiale </t>
-  </si>
-  <si>
-    <t>*DE* Filiale</t>
-  </si>
-  <si>
     <t xml:space="preserve">Partner der Leasingverträge vergibt, die Produkte deshalb als Eigentum hat , sie aber selber nie nutzt.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DE* Partner der Leasingverträge vergibt, die Produkte deshalb als Eigentum hat , sie aber selber nie nutzt. </t>
-  </si>
-  <si>
-    <t>*DE* Finanzierungspartner</t>
   </si>
   <si>
     <t>Lokale Variante einer Sprache
@@ -3393,75 +3363,27 @@
 fr-ca</t>
   </si>
   <si>
-    <t>*DE* Lokale Variante einer Sprache Code wird zusammengesetzt aus ISO2-Sprachcode - ISO2-Landcode  Beispiele: de-de  de-at de-ch fr-ch fr-fr fr-ca</t>
-  </si>
-  <si>
-    <t>*DE* Gebietssprache</t>
-  </si>
-  <si>
     <t>2stellen Sprache Iso, "-", 2 stellen Land-Iso</t>
   </si>
   <si>
-    <t>*DE* ISO-SprachLand_Code</t>
-  </si>
-  <si>
-    <t>*DE* Name [L]</t>
-  </si>
-  <si>
-    <t>*DE* 2stellen Sprache Iso, "-", 2 stellen Land-Iso</t>
-  </si>
-  <si>
     <t>Ein geographisches Gebilde das nach geographischen, polititischen oder postalischen Kriterien in dieser Form definiert ist.</t>
   </si>
   <si>
-    <t>*DE* Ein geographisches Gebilde das nach geographischen, polititischen oder postalischen Kriterien in dieser Form definiert ist.</t>
-  </si>
-  <si>
     <t>Fläche eines Gebiets als geo-Information</t>
   </si>
   <si>
-    <t>*DE* Fläche eines Gebiets als geo-Information</t>
-  </si>
-  <si>
     <t>Rechtlich definierte Einheit, die rechts- und geschäftsfähig ist.</t>
-  </si>
-  <si>
-    <t>*DE* Rechtlich definierte Einheit, die rechts- und geschäftsfähig ist.</t>
-  </si>
-  <si>
-    <t>*DE* Geschäftsfähige Einheit</t>
-  </si>
-  <si>
-    <t>*DE* Name</t>
   </si>
   <si>
     <t>B2B Partner der unsere Produkte und Dienstleistungen weiter verkauft.
 Zwischenhändler, Vermittler, Servicedienstleister, Installateur</t>
   </si>
   <si>
-    <t>*DE* B2B Partner der unsere Produkte und Dienstleistungen weiter verkauft. Zwischenhändler, Vermittler, Servicedienstleister, Installateur</t>
-  </si>
-  <si>
-    <t>*DE* Handelseinheit</t>
-  </si>
-  <si>
     <t>P(rofi), A(-Händler)</t>
-  </si>
-  <si>
-    <t>*DE* Professionalisierungsgrad</t>
-  </si>
-  <si>
-    <t>*DE* P(rofi), A(-Händler)</t>
   </si>
   <si>
     <t xml:space="preserve">Wohneinheit (Adresse + Wohnungsnummer) als Hauptwohnsitz gemeinsam genutzt durch verschiedene  Personen
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DE* Wohneinheit (Adresse + Wohnungsnummer) als Hauptwohnsitz gemeinsam genutzt durch verschiedene  Personen </t>
-  </si>
-  <si>
-    <t>*DE* Haushalt</t>
   </si>
   <si>
     <t>B2B Partner
@@ -3470,20 +3392,8 @@
 B-Händler sind Händler mit niedrigerem Professionalisierungsgrad; verkaufen deshalb nur gewisse Produkte</t>
   </si>
   <si>
-    <t>*DE* B2B Partner Verkauft unsere Produkte an andere Geschäfte. Möglicherweise alleiniger Vertreter in einer geographischen Einheit.  A-Händler sind Händler mit hohem Professionalisierungsgrad, verkaufen alles. B-Händler sind Händler mit niedrigerem Professionalisierungsgrad; verkaufen deshalb nur gewisse Produkte</t>
-  </si>
-  <si>
-    <t>*DE* Händler</t>
-  </si>
-  <si>
     <t>Firma, die unsere Produkte in ein Land importiert.
 Häufig die einzige Firma in einem Land, die diese Rolle übernimmt (Generalimporteur).</t>
-  </si>
-  <si>
-    <t>*DE* Firma, die unsere Produkte in ein Land importiert. Häufig die einzige Firma in einem Land, die diese Rolle übernimmt (Generalimporteur).</t>
-  </si>
-  <si>
-    <t>*DE* Importeur</t>
   </si>
   <si>
     <t>Partner, der die Produkte / Geräte in Betrieb nimmt, montiert, zusammenbaut.
@@ -3492,60 +3402,21 @@
 Handwerker der Geräten (Elektro, Sanitär) in Häusern einbaut</t>
   </si>
   <si>
-    <t>*DE* Partner, der die Produkte / Geräte in Betrieb nimmt, montiert, zusammenbaut.  Beispiele: Montagefirma  Handwerker der Geräten (Elektro, Sanitär) in Häusern einbaut</t>
-  </si>
-  <si>
-    <t>*DE* Installateur</t>
-  </si>
-  <si>
-    <t>*DE* Interessent</t>
-  </si>
-  <si>
     <t>Rechte über das Handelsrecht geregelt.</t>
   </si>
   <si>
-    <t>*DE* Rechte über das Handelsrecht geregelt.</t>
-  </si>
-  <si>
-    <t>*DE* Juristische Person</t>
-  </si>
-  <si>
     <t>Umsatzsteuer-Identifikationsnummer (AT), Ust-IdNr (DE), Unternehmens-Identifikationsnummer (CH)</t>
-  </si>
-  <si>
-    <t>*DE* Gesellschaftsform</t>
-  </si>
-  <si>
-    <t>*DE* UID Nr</t>
-  </si>
-  <si>
-    <t>*DE* Umsatzsteuer-Identifikationsnummer (AT), Ust-IdNr (DE), Unternehmens-Identifikationsnummer (CH)</t>
   </si>
   <si>
     <t xml:space="preserve">Kommunikationskanäle und ihre Adresse
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Kommunikationskanäle und ihre Adresse </t>
-  </si>
-  <si>
     <t>Informationen über Markteilnehmer Partner (Kunden, Lieferanten, Wettberwerber)</t>
-  </si>
-  <si>
-    <t>*DE* Informationen über Markteilnehmer Partner (Kunden, Lieferanten, Wettberwerber)</t>
-  </si>
-  <si>
-    <t>*DE* Kundeninformation</t>
   </si>
   <si>
     <t xml:space="preserve">Geschäftsfähige Einheit, die ein Produkt käuflich erworben hat oder erwerben will.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DE* Geschäftsfähige Einheit, die ein Produkt käuflich erworben hat oder erwerben will. </t>
-  </si>
-  <si>
-    <t>*DE* Käufer</t>
   </si>
   <si>
     <t xml:space="preserve">Land gemäss ISO-Liste ISO-3166-1
@@ -3553,17 +3424,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Land gemäss ISO-Liste ISO-3166-1  Gemäss NUTS (https://de.wikipedia.org/wiki/NUTS) ist das Land die Gebietsstufe NUTS 0 </t>
-  </si>
-  <si>
     <t>Geschäftsfähige Einheit die einen Leasingvertrag für Produkt abgeschlossen hat.
 Damit ist sie Besitzer aber nicht Eigentümer des Produktes</t>
-  </si>
-  <si>
-    <t>*DE* Geschäftsfähige Einheit die einen Leasingvertrag für Produkt abgeschlossen hat. Damit ist sie Besitzer aber nicht Eigentümer des Produktes</t>
-  </si>
-  <si>
-    <t>*DE* Leasingnehmer</t>
   </si>
   <si>
     <t>Eine Zusammenfassung mehrerer Länder zu einer Gruppe.
@@ -3575,9 +3437,6 @@
 EMEA (Europe, Middle East, Africa) (Vertriebsorganisation)</t>
   </si>
   <si>
-    <t>*DE* Eine Zusammenfassung mehrerer Länder zu einer Gruppe. Es soll jeweils ein Kriterium für die Gruppenbildung bzw. einen Begründung (Zweck) für die Nutzung der Gruppe festgelegt/dokumentiert werden.  Typen von Ländergruppen erlauben mehrere Gruppierungen zu führen: Vertriebsorg., Zoll, Logistik   Beispiele: EU SACU Botsuana; Eswatini; Lesotho; Namibia; Südafrika (Zollunion) EMEA (Europe, Middle East, Africa) (Vertriebsorganisation)</t>
-  </si>
-  <si>
     <t>land group</t>
   </si>
   <si>
@@ -3598,12 +3457,6 @@
   <si>
     <t>Geschäftsfähige Einheit, die ein Produkt zum Gebrauch vom Eigentümer mietet.
 Egal ob pay per use  oder Zeitmiete.</t>
-  </si>
-  <si>
-    <t>*DE* Geschäftsfähige Einheit, die ein Produkt zum Gebrauch vom Eigentümer mietet. Egal ob pay per use  oder Zeitmiete.</t>
-  </si>
-  <si>
-    <t>*DE* Mieter</t>
   </si>
   <si>
     <t xml:space="preserve">Nutzer einer Maschine eines Produktes
@@ -3613,21 +3466,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Nutzer einer Maschine eines Produktes  Beispiele Fahrer von Spezalmaschinen Piloten von Flugzeugen </t>
-  </si>
-  <si>
-    <t>*DE* Nutzer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Firmeninterne Organisationeinheit.
 Meist hierarchisch organisiert.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DE* Firmeninterne Organisationeinheit. Meist hierarchisch organisiert. </t>
-  </si>
-  <si>
-    <t>*DE* Organisationseinheit</t>
   </si>
   <si>
     <t xml:space="preserve">Durch die Post vergebene Gebietseinteilung.
@@ -3647,12 +3488,6 @@
     <t>P1-P3</t>
   </si>
   <si>
-    <t>*DE* P1-P3</t>
-  </si>
-  <si>
-    <t>*DE* Partnerinformation</t>
-  </si>
-  <si>
     <t>Beschreibung einer Rolle, die eine Ansprechsperson haben kann.
 Beispiele:
 CEO
@@ -3661,35 +3496,11 @@
 Verkaufsleiter</t>
   </si>
   <si>
-    <t>*DE* Beschreibung einer Rolle, die eine Ansprechsperson haben kann.  Beispiele: CEO CIO Sachdienstmitarbeiter Verkaufsleiter</t>
-  </si>
-  <si>
-    <t>*DE* Personenrolle</t>
-  </si>
-  <si>
-    <t>*DE* Beschreibung</t>
-  </si>
-  <si>
-    <t>*DE* Bezeichnung</t>
-  </si>
-  <si>
     <t>Person oder Firma, von der wir wissen, dass sie sich evtl. für Produkte von CLAAS interessiert.</t>
-  </si>
-  <si>
-    <t>*DE* Person oder Firma, von der wir wissen, dass sie sich evtl. für Produkte von CLAAS interessiert.</t>
-  </si>
-  <si>
-    <t>*DE* Potenzieller Interessent</t>
   </si>
   <si>
     <t xml:space="preserve">Produkte die das Unternehmen vertreibt
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DE* Produkte die das Unternehmen vertreibt </t>
-  </si>
-  <si>
-    <t>*DE* Produktinformation</t>
   </si>
   <si>
     <t xml:space="preserve">einzelnes, weltweit identifizierbares Exemplar eines Produktes.
@@ -3697,53 +3508,17 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* einzelnes, weltweit identifizierbares Exemplar eines Produktes.  Mit oder ohne IOT.  </t>
-  </si>
-  <si>
-    <t>*DE* Produktinstanz</t>
-  </si>
-  <si>
-    <t>*DE* Serie-Nr</t>
-  </si>
-  <si>
     <t>Person, Firma, die sich konkret für ein Produkt interessiert.
 Typischerweise bereits in Verhandlung (Beratung, Angebot, abgeschlossener Vertrag)</t>
   </si>
   <si>
-    <t>*DE* Person, Firma, die sich konkret für ein Produkt interessiert. Typischerweise bereits in Verhandlung (Beratung, Angebot, abgeschlossener Vertrag)</t>
-  </si>
-  <si>
-    <t>*DE* Qualifizierter Interessent</t>
-  </si>
-  <si>
     <t>Partner, der die Produkte / Geräte servisiert (pflegt, repariert, ausbaut, betreut)</t>
   </si>
   <si>
-    <t>*DE* Partner, der die Produkte / Geräte servisiert (pflegt, repariert, ausbaut, betreut)</t>
-  </si>
-  <si>
-    <t>*DE* Servicepartner</t>
-  </si>
-  <si>
     <t>Language</t>
   </si>
   <si>
     <t>Sprache nach ISO-639-1</t>
-  </si>
-  <si>
-    <t>*DE* Sprache nach ISO-639-1</t>
-  </si>
-  <si>
-    <t>*DE* Sprache</t>
-  </si>
-  <si>
-    <t>*DE* Language</t>
-  </si>
-  <si>
-    <t>*DE* ISO2-Code</t>
-  </si>
-  <si>
-    <t>*DE* ISO3-Code</t>
   </si>
   <si>
     <t>Ort an dem die Firma irgendwie vertreten ist
@@ -3753,120 +3528,21 @@
 Bürogebäude</t>
   </si>
   <si>
-    <t>*DE* Ort an dem die Firma irgendwie vertreten ist  Beispiel: Lager Produktionsstätte Bürogebäude</t>
-  </si>
-  <si>
-    <t>*DE* Standort</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ein Kunde ist jemand, der ein Produkt physisch besitzt, aber nicht primär damit Handel treiben , sondern es für den angestammten Zweck nutzen will.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Ein Kunde ist jemand, der ein Produkt physisch besitzt, aber nicht primär damit Handel treiben , sondern es für den angestammten Zweck nutzen will.  </t>
-  </si>
-  <si>
-    <t>*DE* Vertriebskunde</t>
-  </si>
-  <si>
     <t>B2B Vertriebsteilnehmer, der unsere Produkte weiter verkauft oder vermittelt</t>
-  </si>
-  <si>
-    <t>*DE* B2B Vertriebsteilnehmer, der unsere Produkte weiter verkauft oder vermittelt</t>
-  </si>
-  <si>
-    <t>*DE* Vertriebspartner</t>
   </si>
   <si>
     <t xml:space="preserve">Ein Marktteilnehmer, der mit verkaufbaren oder vermietbaren Produkten von uns direkt oder indirekt zu tun hat.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Ein Marktteilnehmer, der mit verkaufbaren oder vermietbaren Produkten von uns direkt oder indirekt zu tun hat.  </t>
-  </si>
-  <si>
-    <t>*DE* Vertriebsteilnehmer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Firma die ähnliche Produkte anbietet oder herstellt und oder ähnliche Kundensegmente betreut
 </t>
   </si>
   <si>
-    <t xml:space="preserve">*DE* Firma die ähnliche Produkte anbietet oder herstellt und oder ähnliche Kundensegmente betreut </t>
-  </si>
-  <si>
-    <t>*DE* Wettbewerber</t>
-  </si>
-  <si>
-    <t>*DE* bild1</t>
-  </si>
-  <si>
-    <t>*DE* bild1v1</t>
-  </si>
-  <si>
-    <t>*DE* bild1v2</t>
-  </si>
-  <si>
-    <t>*DE* bild1v3</t>
-  </si>
-  <si>
-    <t>*DE* bild1v4</t>
-  </si>
-  <si>
-    <t>*DE* bild1v5</t>
-  </si>
-  <si>
-    <t>*DE* bild1v6</t>
-  </si>
-  <si>
-    <t>*DE* bild1v6v1</t>
-  </si>
-  <si>
-    <t>*DE* bild1v6v1v1</t>
-  </si>
-  <si>
-    <t>*DE* bild1v6v1v2</t>
-  </si>
-  <si>
-    <t>*DE* bild1v7</t>
-  </si>
-  <si>
-    <t>*DE* bild1v7v1</t>
-  </si>
-  <si>
-    <t>*DE* bild1v7v2</t>
-  </si>
-  <si>
-    <t>*DE* bild1v7v3</t>
-  </si>
-  <si>
-    <t>*DE* bild2</t>
-  </si>
-  <si>
-    <t>*DE* bild3</t>
-  </si>
-  <si>
-    <t>*DE* bild4</t>
-  </si>
-  <si>
-    <t>*DE* bild4v1</t>
-  </si>
-  <si>
-    <t>*DE* natürliche Person</t>
-  </si>
-  <si>
-    <t>*DE* Geburtsdatum</t>
-  </si>
-  <si>
-    <t>*DE* Geschlecht</t>
-  </si>
-  <si>
-    <t>*DE* Vorname</t>
-  </si>
-  <si>
-    <t>*DE* test</t>
-  </si>
-  <si>
     <t>Territorial division of a country into smaller units. According to NUTS (https://en.wikipedia.org/wiki/NUTS) the country is the NUTS 0 NUTS 0 national state NUTS 1 "major socio-economic regions (grouping basic regions)" ... larger regions / districts NUTS 2 "basic regions (for the application of regional policies) "... medium-sized regions, megacities NUTS 3" small regions (for specific diagnoses) "... smaller regions, some already big cities LAU 1 oA ... municipal administrative associations, partly municipalities (not defined in all states) LAU 2 "municipalities or equivalent units" ... municipalities, partly church affiliations There can be further hierarchical level designations: Germany A0: Country A1: Federal state A2: empty A3: County A4: empty A5: Municipality: Administrative municipality in the respective country Field names, municipalities, old municipality names (subdivide municipality) or further stages</t>
   </si>
   <si>
@@ -3937,6 +3613,345 @@
   </si>
   <si>
     <t>County</t>
+  </si>
+  <si>
+    <t>**Purpose of the address (financial, postal, delivery, etc.)</t>
+  </si>
+  <si>
+    <t>**A person or company that acts as a broker for us (in an area). Does not deal with the goods in this role itself. So it has neither a warehouse nor is it an addressee of deliveries.</t>
+  </si>
+  <si>
+    <t>**Agent</t>
+  </si>
+  <si>
+    <t>**Master information that is valid beyond a company or that is specified by standards.</t>
+  </si>
+  <si>
+    <t>**General Information</t>
+  </si>
+  <si>
+    <t>**Function of a person for a legal entity. In a special case, a person can be your own contact person as a sole proprietorship.  26.6.18 - THU: contact person's name changed to contact person's name Synonym changed from contact person's name to contact person's name</t>
+  </si>
+  <si>
+    <t>**Contact for</t>
+  </si>
+  <si>
+    <t>**Contact</t>
+  </si>
+  <si>
+    <t>**Validity period</t>
+  </si>
+  <si>
+    <t>**Person or company that has a machine in its physical possession.</t>
+  </si>
+  <si>
+    <t>**Owner</t>
+  </si>
+  <si>
+    <t>**Person, organisation legally owning machine copies.</t>
+  </si>
+  <si>
+    <t>**B2C Retail unit Business, local, branch</t>
+  </si>
+  <si>
+    <t>**Branch</t>
+  </si>
+  <si>
+    <t>**A partner who awards leasing contracts, who therefore owns the products, but never uses them himself</t>
+  </si>
+  <si>
+    <t>**Financing partner</t>
+  </si>
+  <si>
+    <t>**The territorial division of a country into smaller units.  According to NUTS (https://de.wikipedia.org/wiki/NUTS) the country is the territorial level NUTS 0 NUTS 0 National state NUTS 1 "major socio-economic regions (grouping basic regions)" ... larger regions NUTS 2 "basic regions (for the application of regional policies)" ... medium-sized regions, megacities NUTS 3 "small regions (for specific diagnoses)" ... smaller regions, some already big cities LAU 1 o.LAU 2 "municipalities or equivalent units" ... Municipalities, partly municipal subdivisions There may be further hierarchy level designations: Germany A0: Country A1: Federal state A2: empty A3: Administrative district A4: empty A5: Municipality: Administrative municipality in the respective country Field names, municipal areas, old municipality names (subdivide municipality) or further levels</t>
+  </si>
+  <si>
+    <t>**Local variant of a language code is composed of ISO2 language code - ISO2 country code examples: de-de-de-at de-ch fr-ch fr-fr fr-ca</t>
+  </si>
+  <si>
+    <t>**Regional language</t>
+  </si>
+  <si>
+    <t>**ISO LanguageCountry_Code</t>
+  </si>
+  <si>
+    <t>**2 digits Language Iso, "-", 2 digits Country Iso</t>
+  </si>
+  <si>
+    <t>**Name [L]</t>
+  </si>
+  <si>
+    <t>**A geographical entity defined in this form according to geographical, political or postal criteria.</t>
+  </si>
+  <si>
+    <t>**Area of an area as geo-information</t>
+  </si>
+  <si>
+    <t>**Legally defined unit that is legally and legally capable.</t>
+  </si>
+  <si>
+    <t>**Unit with legal capacity</t>
+  </si>
+  <si>
+    <t>**Name</t>
+  </si>
+  <si>
+    <t>**B2B partner who resells our products and services. Intermediary, intermediary, service provider, installer</t>
+  </si>
+  <si>
+    <t>**Trade unit</t>
+  </si>
+  <si>
+    <t>**Degree of professionalization</t>
+  </si>
+  <si>
+    <t>**P(rofi), A(-dealer)</t>
+  </si>
+  <si>
+    <t>**Housing unit (address + apartment number) as main residence shared by different persons</t>
+  </si>
+  <si>
+    <t>**Household</t>
+  </si>
+  <si>
+    <t>**B2B Partner Sells our products to other stores. Possibly sole representative in a geographical unit.  A dealers are dealers with high degree of professionalization, sell everything. B dealers are dealers with a lower degree of professionalization; therefore only sell certain products</t>
+  </si>
+  <si>
+    <t>**Dealer</t>
+  </si>
+  <si>
+    <t>**Company that imports our products into a country. Often the only company in a country that assumes this role (general importer).</t>
+  </si>
+  <si>
+    <t>**Importer</t>
+  </si>
+  <si>
+    <t>**Partner who commissions, assembles and assembles the products / devices.  Examples: Company assembling craftsmen of devices (electric, sanitary) built into houses</t>
+  </si>
+  <si>
+    <t>**Plumber</t>
+  </si>
+  <si>
+    <t>**Prospective customer</t>
+  </si>
+  <si>
+    <t>**Rights are regulated by commercial law.</t>
+  </si>
+  <si>
+    <t>**Legal person</t>
+  </si>
+  <si>
+    <t>**Form of society</t>
+  </si>
+  <si>
+    <t>**UID No</t>
+  </si>
+  <si>
+    <t>**Value added tax identification number (AT), VAT ID number (DE), company identification number (CH)</t>
+  </si>
+  <si>
+    <t>**Communication channels and their addresses</t>
+  </si>
+  <si>
+    <t>**Information about market participants Partners (customers, suppliers, competitors)</t>
+  </si>
+  <si>
+    <t>**Customer information</t>
+  </si>
+  <si>
+    <t>**Legal entity that has acquired or intends to acquire a product by way of purchase</t>
+  </si>
+  <si>
+    <t>**Shopper</t>
+  </si>
+  <si>
+    <t>**Country according to ISO list ISO-3166-1 According to NUTS (https://de.wikipedia.org/wiki/NUTS), the country is the territorial level NUTS 0</t>
+  </si>
+  <si>
+    <t>**Legal entity that has concluded a leasing contract for a product. It is the owner but not the owner of the product</t>
+  </si>
+  <si>
+    <t>**Lessee</t>
+  </si>
+  <si>
+    <t>**A grouping of several countries into one group. A criterion for group formation or a justification (purpose) for the use of the group should be defined/documented in each case.  Types of country groups allow you to manage several groupings: Sales org., customs, logistics examples: EU SACU Botswana; Eswatini; Lesotho; Namibia; South Africa (Customs Union) EMEA (Europe, Middle East, Africa) (Sales Organization)</t>
+  </si>
+  <si>
+    <t>**Business entity that rents a product for use by its owner. Whether pay per use or time rental.</t>
+  </si>
+  <si>
+    <t>**Users of a machine of a product Examples Drivers of special machines Pilots of aircraft</t>
+  </si>
+  <si>
+    <t>**User</t>
+  </si>
+  <si>
+    <t>**Internal company organizational unit. Mostly organized hierarchically</t>
+  </si>
+  <si>
+    <t>**Organizational unit</t>
+  </si>
+  <si>
+    <t>**P1-P3</t>
+  </si>
+  <si>
+    <t>**Partner information</t>
+  </si>
+  <si>
+    <t>**Description of a role that a contact person can have.  Examples: CEO CIO Sales Manager</t>
+  </si>
+  <si>
+    <t>**Person role</t>
+  </si>
+  <si>
+    <t>**Description of the</t>
+  </si>
+  <si>
+    <t>**Designation</t>
+  </si>
+  <si>
+    <t>**Person or company that we know may be interested in CLAAS products.</t>
+  </si>
+  <si>
+    <t>**Potential interested party</t>
+  </si>
+  <si>
+    <t>**Products that the company distributes</t>
+  </si>
+  <si>
+    <t>**Product information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**single, globally identifiable copy of a product.  With or without IOT.  </t>
+  </si>
+  <si>
+    <t>**Product instance</t>
+  </si>
+  <si>
+    <t>**Series No</t>
+  </si>
+  <si>
+    <t>**Person, company that is specifically interested in a product. Typically already in negotiation (consultation, offer, concluded contract)</t>
+  </si>
+  <si>
+    <t>**Qualified interested party</t>
+  </si>
+  <si>
+    <t>**Partner who services the products / devices (maintains, repairs, removes, supports)</t>
+  </si>
+  <si>
+    <t>**Service partner</t>
+  </si>
+  <si>
+    <t>**Language according to ISO-639-1</t>
+  </si>
+  <si>
+    <t>**Language</t>
+  </si>
+  <si>
+    <t>**ISO2 code</t>
+  </si>
+  <si>
+    <t>**ISO3 code</t>
+  </si>
+  <si>
+    <t>**Place where the company is somehow represented Example: Warehouse Production site Office building</t>
+  </si>
+  <si>
+    <t>**Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**A customer is someone who owns a product physically, but does not primarily trade with it, but wants to use it for its original purpose.  </t>
+  </si>
+  <si>
+    <t>**Distribution customer</t>
+  </si>
+  <si>
+    <t>**B2B sales participant who resells or brokers our products</t>
+  </si>
+  <si>
+    <t>**Sales partners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**A market participant who deals directly or indirectly with our saleable or rentable products.  </t>
+  </si>
+  <si>
+    <t>**Distribution participants</t>
+  </si>
+  <si>
+    <t>**Company that offers or manufactures similar products and services similar customer segments</t>
+  </si>
+  <si>
+    <t>**Competitor</t>
+  </si>
+  <si>
+    <t>**picture1</t>
+  </si>
+  <si>
+    <t>**picture1v1</t>
+  </si>
+  <si>
+    <t>**picture1v2</t>
+  </si>
+  <si>
+    <t>**picture1v3</t>
+  </si>
+  <si>
+    <t>**picture1v4</t>
+  </si>
+  <si>
+    <t>**picture1v5</t>
+  </si>
+  <si>
+    <t>**picture1v6</t>
+  </si>
+  <si>
+    <t>**picture1v6v1</t>
+  </si>
+  <si>
+    <t>**picture1v6v1v1</t>
+  </si>
+  <si>
+    <t>**picture1v6v1v2</t>
+  </si>
+  <si>
+    <t>**picture1v7</t>
+  </si>
+  <si>
+    <t>**picture1v7v1</t>
+  </si>
+  <si>
+    <t>**picture1v7v2</t>
+  </si>
+  <si>
+    <t>**picture1v7v3</t>
+  </si>
+  <si>
+    <t>**picture2</t>
+  </si>
+  <si>
+    <t>**picture3</t>
+  </si>
+  <si>
+    <t>**picture4</t>
+  </si>
+  <si>
+    <t>**picture4v1</t>
+  </si>
+  <si>
+    <t>**natural person</t>
+  </si>
+  <si>
+    <t>**Date of birth</t>
+  </si>
+  <si>
+    <t>**Sex</t>
+  </si>
+  <si>
+    <t>**First name</t>
+  </si>
+  <si>
+    <t>**test</t>
   </si>
 </sst>
 </file>
@@ -4022,7 +4037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4040,10 +4055,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4372,17 +4401,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4391,25 +4420,25 @@
       <c r="B4" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4420,72 +4449,99 @@
       <c r="B5" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>718</v>
-      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>547</v>
-      </c>
+      <c r="E9" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -4494,25 +4550,25 @@
       <c r="B11" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4523,152 +4579,161 @@
       <c r="B12" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="C12" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>550</v>
-      </c>
+      <c r="E16" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="10"/>
+      <c r="D18" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="10"/>
+      <c r="D19" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="10"/>
+      <c r="D20" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4677,25 +4742,25 @@
       <c r="B22" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4706,27 +4771,23 @@
       <c r="B23" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="C23" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4735,25 +4796,25 @@
       <c r="B24" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4764,27 +4825,23 @@
       <c r="B25" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="C25" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -4793,25 +4850,25 @@
       <c r="B26" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4820,74 +4877,97 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="E27" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>561</v>
-      </c>
+      <c r="F27" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="C31" s="10"/>
+      <c r="D31" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -4896,25 +4976,25 @@
       <c r="B33" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4925,27 +5005,23 @@
       <c r="B34" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="C34" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
@@ -4954,25 +5030,25 @@
       <c r="B35" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4983,27 +5059,23 @@
       <c r="B36" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="C36" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
@@ -5012,25 +5084,25 @@
       <c r="B37" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5041,27 +5113,23 @@
       <c r="B38" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="C38" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="E38" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
@@ -5070,25 +5138,25 @@
       <c r="B39" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5099,27 +5167,23 @@
       <c r="B40" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="C40" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="E40" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="I40" s="10"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -5128,25 +5192,25 @@
       <c r="B41" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5157,27 +5221,23 @@
       <c r="B42" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
@@ -5186,25 +5246,25 @@
       <c r="B43" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5215,92 +5275,113 @@
       <c r="B44" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="C44" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="E44" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="C48" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>581</v>
-      </c>
+      <c r="E48" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="C49" s="10"/>
+      <c r="D49" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -5309,25 +5390,25 @@
       <c r="B51" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5338,92 +5419,113 @@
       <c r="B52" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="C52" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="I52" s="10"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="C56" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="F56" s="5" t="s">
+      <c r="E56" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>585</v>
-      </c>
+      <c r="G56" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="C57" s="10"/>
+      <c r="D57" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F57" s="5" t="s">
+      <c r="E57" s="12"/>
+      <c r="F57" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="G57" s="12"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
@@ -5432,25 +5534,25 @@
       <c r="B59" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5461,72 +5563,91 @@
       <c r="B60" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="C60" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="E60" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="I60" s="10"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
     </row>
     <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D64" s="5" t="s">
+      <c r="C64" s="10"/>
+      <c r="D64" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="G64" s="12"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
@@ -5535,25 +5656,25 @@
       <c r="B66" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5564,72 +5685,97 @@
       <c r="B67" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="C67" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="I67" s="10"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
     </row>
     <row r="69" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="D71" s="5" t="s">
+      <c r="C71" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>595</v>
-      </c>
+      <c r="E71" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
     </row>
     <row r="73" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
@@ -5638,25 +5784,25 @@
       <c r="B73" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5667,27 +5813,23 @@
       <c r="B74" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="E74" s="4" t="s">
+      <c r="C74" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="E74" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="I74" s="10"/>
     </row>
     <row r="75" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
@@ -5696,25 +5838,25 @@
       <c r="B75" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5725,27 +5867,23 @@
       <c r="B76" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="C76" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="I76" s="10"/>
     </row>
     <row r="77" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
@@ -5754,25 +5892,25 @@
       <c r="B77" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5783,27 +5921,23 @@
       <c r="B78" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="C78" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="I78" s="10"/>
     </row>
     <row r="79" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
@@ -5812,25 +5946,25 @@
       <c r="B79" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5841,27 +5975,23 @@
       <c r="B80" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="C80" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="I80" s="10"/>
     </row>
     <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
@@ -5870,25 +6000,25 @@
       <c r="B81" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5899,27 +6029,17 @@
       <c r="B82" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E82" s="4" t="s">
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="I82" s="10"/>
     </row>
     <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
@@ -5928,25 +6048,25 @@
       <c r="B83" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="I83" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5957,92 +6077,113 @@
       <c r="B84" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="E84" s="4" t="s">
+      <c r="C84" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F84" s="10"/>
+      <c r="G84" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="I84" s="10"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D88" s="5" t="s">
+      <c r="C88" s="10"/>
+      <c r="D88" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="G88" s="12"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="D89" s="5" t="s">
+      <c r="C89" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>615</v>
-      </c>
+      <c r="E89" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
@@ -6051,25 +6192,25 @@
       <c r="B91" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="I91" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6080,132 +6221,139 @@
       <c r="B92" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E92" s="4" t="s">
+      <c r="C92" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="E92" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G92" s="4" t="s">
+      <c r="F92" s="10"/>
+      <c r="G92" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="H92" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="H92" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="I92" s="10"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D96" s="5" t="s">
+      <c r="C96" s="10"/>
+      <c r="D96" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D97" s="5" t="s">
+      <c r="C97" s="10"/>
+      <c r="D97" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="G97" s="12"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D98" s="5" t="s">
+      <c r="C98" s="10"/>
+      <c r="D98" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="G98" s="12"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D99" s="5" t="s">
+      <c r="C99" s="10"/>
+      <c r="D99" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F99" s="5" t="s">
+      <c r="E99" s="12"/>
+      <c r="F99" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="G99" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="G99" s="12"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
@@ -6214,25 +6362,25 @@
       <c r="B101" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I101" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6243,27 +6391,23 @@
       <c r="B102" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E102" s="4" t="s">
+      <c r="C102" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="E102" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="I102" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F102" s="10"/>
+      <c r="G102" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="I102" s="10"/>
     </row>
     <row r="103" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
@@ -6272,25 +6416,25 @@
       <c r="B103" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F103" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="G103" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H103" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I103" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6301,27 +6445,23 @@
       <c r="B104" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="E104" s="4" t="s">
+      <c r="C104" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="E104" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F104" s="10"/>
+      <c r="G104" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="I104" s="10"/>
     </row>
     <row r="105" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
@@ -6330,25 +6470,25 @@
       <c r="B105" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G105" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H105" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I105" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6359,132 +6499,139 @@
       <c r="B106" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E106" s="4" t="s">
+      <c r="C106" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E106" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="H106" s="4" t="s">
+      <c r="F106" s="10"/>
+      <c r="G106" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="H106" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="I106" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="I106" s="10"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="F109" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="G109" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D110" s="5" t="s">
+      <c r="C110" s="10"/>
+      <c r="D110" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F110" s="5" t="s">
+      <c r="E110" s="12"/>
+      <c r="F110" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="G110" s="12"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
     </row>
     <row r="111" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D111" s="5" t="s">
+      <c r="C111" s="10"/>
+      <c r="D111" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F111" s="5" t="s">
+      <c r="E111" s="12"/>
+      <c r="F111" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G111" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="G111" s="12"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C112" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D112" s="5" t="s">
+      <c r="C112" s="10"/>
+      <c r="D112" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="G112" s="12"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D113" s="5" t="s">
+      <c r="C113" s="10"/>
+      <c r="D113" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F113" s="5" t="s">
+      <c r="E113" s="12"/>
+      <c r="F113" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="G113" s="12"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
@@ -6493,25 +6640,25 @@
       <c r="B115" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G115" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="I115" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6522,27 +6669,23 @@
       <c r="B116" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="E116" s="4" t="s">
+      <c r="C116" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="E116" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F116" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="I116" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F116" s="10"/>
+      <c r="G116" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="I116" s="10"/>
     </row>
     <row r="117" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
@@ -6551,25 +6694,25 @@
       <c r="B117" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F117" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G117" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="H117" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="I117" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6580,92 +6723,115 @@
       <c r="B118" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="E118" s="4" t="s">
+      <c r="C118" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E118" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F118" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="I118" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F118" s="10"/>
+      <c r="G118" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="I118" s="10"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
     </row>
     <row r="121" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E121" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="F121" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="G121" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D122" s="5" t="s">
+      <c r="C122" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="D122" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="E122" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>635</v>
-      </c>
+      <c r="E122" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D123" s="5" t="s">
+      <c r="C123" s="10"/>
+      <c r="D123" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E123" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>636</v>
-      </c>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="H123" s="6"/>
+      <c r="I123" s="6"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
@@ -6674,25 +6840,25 @@
       <c r="B125" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="G125" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="H125" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="I125" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6703,27 +6869,23 @@
       <c r="B126" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="E126" s="4" t="s">
+      <c r="C126" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F126" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="I126" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F126" s="10"/>
+      <c r="G126" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="I126" s="10"/>
     </row>
     <row r="127" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
@@ -6732,25 +6894,25 @@
       <c r="B127" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="G127" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H127" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="I127" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6761,27 +6923,23 @@
       <c r="B128" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="E128" s="4" t="s">
+      <c r="C128" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="E128" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F128" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="I128" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="I128" s="10"/>
     </row>
     <row r="129" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
@@ -6790,25 +6948,25 @@
       <c r="B129" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G129" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="I129" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6819,72 +6977,91 @@
       <c r="B130" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C130" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="E130" s="4" t="s">
+      <c r="C130" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E130" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F130" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="I130" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F130" s="10"/>
+      <c r="G130" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I130" s="10"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C131" s="6"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="6"/>
     </row>
     <row r="132" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F133" s="2" t="s">
+      <c r="F133" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="G133" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C134" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D134" s="5" t="s">
+      <c r="C134" s="10"/>
+      <c r="D134" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E134" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="G134" s="12"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
@@ -6893,25 +7070,25 @@
       <c r="B136" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G136" s="1" t="s">
+      <c r="G136" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="H136" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="I136" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6920,94 +7097,117 @@
         <v>117</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="E137" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F137" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="I137" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F137" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="I137" s="10"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B140" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E140" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="F140" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B141" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="D141" s="5" t="s">
+      <c r="C141" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D141" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="E141" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>648</v>
-      </c>
+      <c r="E141" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="G141" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B142" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D142" s="5" t="s">
+      <c r="C142" s="10"/>
+      <c r="D142" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="E142" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="G142" s="12"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C143" s="6"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
     </row>
     <row r="144" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
@@ -7016,25 +7216,25 @@
       <c r="B144" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G144" s="1" t="s">
+      <c r="G144" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="H144" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="I144" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7045,27 +7245,23 @@
       <c r="B145" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E145" s="4" t="s">
+      <c r="C145" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="E145" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F145" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="I145" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="I145" s="10"/>
     </row>
     <row r="146" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
@@ -7074,25 +7270,25 @@
       <c r="B146" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F146" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G146" s="1" t="s">
+      <c r="G146" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="H146" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="I146" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7103,92 +7299,107 @@
       <c r="B147" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="E147" s="4" t="s">
+      <c r="C147" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="E147" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F147" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="I147" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="I147" s="10"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="6"/>
     </row>
     <row r="149" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B149" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
     </row>
     <row r="150" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B150" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="F150" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="G150" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H150" s="6"/>
+      <c r="I150" s="6"/>
     </row>
     <row r="151" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B151" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C151" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D151" s="5" t="s">
+      <c r="C151" s="10"/>
+      <c r="D151" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E151" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="G151" s="12"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6"/>
     </row>
     <row r="152" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B152" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C152" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D152" s="5" t="s">
+      <c r="C152" s="10"/>
+      <c r="D152" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E152" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E152" s="12"/>
+      <c r="F152" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="G152" s="12"/>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6"/>
     </row>
     <row r="154" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
@@ -7197,25 +7408,25 @@
       <c r="B154" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D154" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E154" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F154" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G154" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="H154" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="I154" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7226,27 +7437,23 @@
       <c r="B155" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="E155" s="4" t="s">
+      <c r="C155" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="E155" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F155" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="I155" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="I155" s="10"/>
     </row>
     <row r="156" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
@@ -7255,25 +7462,25 @@
       <c r="B156" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C156" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D156" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="E156" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F156" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G156" s="1" t="s">
+      <c r="G156" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="H156" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="I156" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7284,27 +7491,23 @@
       <c r="B157" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C157" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="E157" s="4" t="s">
+      <c r="C157" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="E157" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F157" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G157" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="H157" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="I157" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F157" s="10"/>
+      <c r="G157" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="I157" s="10"/>
     </row>
     <row r="158" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
@@ -7313,25 +7516,25 @@
       <c r="B158" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="E158" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="F158" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G158" s="1" t="s">
+      <c r="G158" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H158" s="1" t="s">
+      <c r="H158" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I158" s="1" t="s">
+      <c r="I158" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7342,72 +7545,91 @@
       <c r="B159" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C159" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="E159" s="4" t="s">
+      <c r="C159" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="E159" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="F159" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="I159" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F159" s="10"/>
+      <c r="G159" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="I159" s="10"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C160" s="6"/>
+      <c r="D160" s="6"/>
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
+      <c r="G160" s="6"/>
+      <c r="H160" s="6"/>
+      <c r="I160" s="6"/>
     </row>
     <row r="161" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B161" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C161" s="6"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="6"/>
+      <c r="F161" s="6"/>
+      <c r="G161" s="6"/>
+      <c r="H161" s="6"/>
+      <c r="I161" s="6"/>
     </row>
     <row r="162" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E162" s="2" t="s">
+      <c r="E162" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="F162" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H162" s="6"/>
+      <c r="I162" s="6"/>
     </row>
     <row r="163" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C163" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D163" s="5" t="s">
+      <c r="C163" s="10"/>
+      <c r="D163" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="E163" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E163" s="12"/>
+      <c r="F163" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="G163" s="12"/>
+      <c r="H163" s="6"/>
+      <c r="I163" s="6"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C164" s="6"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+      <c r="G164" s="6"/>
+      <c r="H164" s="6"/>
+      <c r="I164" s="6"/>
     </row>
     <row r="165" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
@@ -7416,25 +7638,25 @@
       <c r="B165" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C165" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D165" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="E165" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="F165" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="G165" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="H165" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="I165" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7445,27 +7667,23 @@
       <c r="B166" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="E166" s="4" t="s">
+      <c r="C166" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="E166" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F166" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G166" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="H166" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="I166" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F166" s="10"/>
+      <c r="G166" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="I166" s="10"/>
     </row>
     <row r="167" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
@@ -7474,25 +7692,25 @@
       <c r="B167" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="C167" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D167" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E167" s="1" t="s">
+      <c r="E167" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F167" s="1" t="s">
+      <c r="F167" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G167" s="1" t="s">
+      <c r="G167" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="H167" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I167" s="1" t="s">
+      <c r="I167" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7503,27 +7721,23 @@
       <c r="B168" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C168" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="E168" s="4" t="s">
+      <c r="C168" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E168" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F168" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G168" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="H168" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="I168" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F168" s="10"/>
+      <c r="G168" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="I168" s="10"/>
     </row>
     <row r="169" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
@@ -7532,25 +7746,25 @@
       <c r="B169" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C169" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D169" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E169" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F169" s="1" t="s">
+      <c r="F169" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="G169" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="H169" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="I169" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7559,114 +7773,129 @@
         <v>129</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="E170" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="E170" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F170" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G170" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="H170" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="I170" s="4" t="s">
-        <v>675</v>
-      </c>
+      <c r="F170" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="I170" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="6"/>
+      <c r="H171" s="6"/>
+      <c r="I171" s="6"/>
     </row>
     <row r="172" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B172" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="6"/>
+      <c r="H172" s="6"/>
+      <c r="I172" s="6"/>
     </row>
     <row r="173" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B173" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C173" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D173" s="2" t="s">
+      <c r="D173" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="E173" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="F173" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G173" s="2" t="s">
+      <c r="G173" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H173" s="6"/>
+      <c r="I173" s="6"/>
     </row>
     <row r="174" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B174" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C174" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D174" s="5" t="s">
+      <c r="C174" s="10"/>
+      <c r="D174" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="G174" s="12"/>
+      <c r="H174" s="6"/>
+      <c r="I174" s="6"/>
     </row>
     <row r="175" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B175" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C175" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D175" s="5" t="s">
+      <c r="C175" s="10"/>
+      <c r="D175" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="E175" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="G175" s="12"/>
+      <c r="H175" s="6"/>
+      <c r="I175" s="6"/>
     </row>
     <row r="176" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B176" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C176" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D176" s="5" t="s">
+      <c r="C176" s="10"/>
+      <c r="D176" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E176" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="G176" s="12"/>
+      <c r="H176" s="6"/>
+      <c r="I176" s="6"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6"/>
+      <c r="H177" s="6"/>
+      <c r="I177" s="6"/>
     </row>
     <row r="178" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
@@ -7675,25 +7904,25 @@
       <c r="B178" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="C178" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D178" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E178" s="1" t="s">
+      <c r="E178" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F178" s="1" t="s">
+      <c r="F178" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G178" s="1" t="s">
+      <c r="G178" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H178" s="1" t="s">
+      <c r="H178" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I178" s="1" t="s">
+      <c r="I178" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7704,72 +7933,91 @@
       <c r="B179" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C179" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="E179" s="4" t="s">
+      <c r="C179" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="E179" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F179" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="H179" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="I179" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F179" s="10"/>
+      <c r="G179" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="H179" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="I179" s="10"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="6"/>
+      <c r="H180" s="6"/>
+      <c r="I180" s="6"/>
     </row>
     <row r="181" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B181" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6"/>
+      <c r="H181" s="6"/>
+      <c r="I181" s="6"/>
     </row>
     <row r="182" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="D182" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="E182" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F182" s="2" t="s">
+      <c r="F182" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H182" s="6"/>
+      <c r="I182" s="6"/>
     </row>
     <row r="183" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C183" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D183" s="5" t="s">
+      <c r="C183" s="10"/>
+      <c r="D183" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E183" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="G183" s="12"/>
+      <c r="H183" s="6"/>
+      <c r="I183" s="6"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C184" s="6"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+      <c r="G184" s="6"/>
+      <c r="H184" s="6"/>
+      <c r="I184" s="6"/>
     </row>
     <row r="185" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
@@ -7778,25 +8026,25 @@
       <c r="B185" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="C185" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D185" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E185" s="1" t="s">
+      <c r="E185" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F185" s="1" t="s">
+      <c r="F185" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G185" s="1" t="s">
+      <c r="G185" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H185" s="1" t="s">
+      <c r="H185" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I185" s="1" t="s">
+      <c r="I185" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7807,27 +8055,23 @@
       <c r="B186" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C186" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="E186" s="4" t="s">
+      <c r="C186" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="E186" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F186" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G186" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="H186" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="I186" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F186" s="10"/>
+      <c r="G186" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="H186" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="I186" s="10"/>
     </row>
     <row r="187" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
@@ -7836,25 +8080,25 @@
       <c r="B187" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="C187" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="D187" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E187" s="1" t="s">
+      <c r="E187" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="F187" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G187" s="1" t="s">
+      <c r="G187" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H187" s="1" t="s">
+      <c r="H187" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I187" s="1" t="s">
+      <c r="I187" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7865,27 +8109,23 @@
       <c r="B188" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="D188" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="E188" s="4" t="s">
+      <c r="C188" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="E188" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="F188" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G188" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="H188" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="I188" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F188" s="10"/>
+      <c r="G188" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="H188" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="I188" s="10"/>
     </row>
     <row r="189" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
@@ -7894,25 +8134,25 @@
       <c r="B189" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C189" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D189" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="E189" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F189" s="1" t="s">
+      <c r="F189" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G189" s="1" t="s">
+      <c r="G189" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H189" s="1" t="s">
+      <c r="H189" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I189" s="1" t="s">
+      <c r="I189" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7923,27 +8163,23 @@
       <c r="B190" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C190" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="E190" s="4" t="s">
+      <c r="C190" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="D190" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="E190" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F190" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G190" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="H190" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="I190" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F190" s="10"/>
+      <c r="G190" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="I190" s="10"/>
     </row>
     <row r="191" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
@@ -7952,25 +8188,25 @@
       <c r="B191" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="C191" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="D191" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E191" s="1" t="s">
+      <c r="E191" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F191" s="1" t="s">
+      <c r="F191" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G191" s="1" t="s">
+      <c r="G191" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H191" s="1" t="s">
+      <c r="H191" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I191" s="1" t="s">
+      <c r="I191" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7981,27 +8217,23 @@
       <c r="B192" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C192" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="E192" s="4" t="s">
+      <c r="C192" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="E192" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F192" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G192" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="H192" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="I192" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F192" s="10"/>
+      <c r="G192" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="H192" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="I192" s="10"/>
     </row>
     <row r="193" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
@@ -8010,25 +8242,25 @@
       <c r="B193" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="C193" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="D193" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E193" s="1" t="s">
+      <c r="E193" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F193" s="1" t="s">
+      <c r="F193" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G193" s="1" t="s">
+      <c r="G193" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H193" s="1" t="s">
+      <c r="H193" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I193" s="1" t="s">
+      <c r="I193" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8039,27 +8271,17 @@
       <c r="B194" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C194" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D194" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E194" s="4" t="s">
+      <c r="C194" s="10"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F194" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G194" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H194" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="I194" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F194" s="10"/>
+      <c r="G194" s="10"/>
+      <c r="H194" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="I194" s="10"/>
     </row>
     <row r="195" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
@@ -8068,25 +8290,25 @@
       <c r="B195" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="C195" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E195" s="1" t="s">
+      <c r="E195" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F195" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G195" s="1" t="s">
+      <c r="G195" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H195" s="1" t="s">
+      <c r="H195" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I195" s="1" t="s">
+      <c r="I195" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8097,27 +8319,17 @@
       <c r="B196" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C196" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D196" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E196" s="4" t="s">
+      <c r="C196" s="10"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F196" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G196" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H196" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="I196" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F196" s="10"/>
+      <c r="G196" s="10"/>
+      <c r="H196" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="I196" s="10"/>
     </row>
     <row r="197" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
@@ -8126,25 +8338,25 @@
       <c r="B197" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="C197" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="D197" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E197" s="1" t="s">
+      <c r="E197" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F197" s="1" t="s">
+      <c r="F197" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G197" s="1" t="s">
+      <c r="G197" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H197" s="1" t="s">
+      <c r="H197" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I197" s="1" t="s">
+      <c r="I197" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8155,27 +8367,17 @@
       <c r="B198" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C198" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E198" s="4" t="s">
+      <c r="C198" s="10"/>
+      <c r="D198" s="10"/>
+      <c r="E198" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F198" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G198" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H198" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="I198" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F198" s="10"/>
+      <c r="G198" s="10"/>
+      <c r="H198" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="I198" s="10"/>
     </row>
     <row r="199" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
@@ -8184,25 +8386,25 @@
       <c r="B199" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="C199" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D199" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E199" s="1" t="s">
+      <c r="E199" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F199" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H199" s="1" t="s">
+      <c r="H199" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I199" s="1" t="s">
+      <c r="I199" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8213,27 +8415,17 @@
       <c r="B200" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C200" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D200" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E200" s="4" t="s">
+      <c r="C200" s="10"/>
+      <c r="D200" s="10"/>
+      <c r="E200" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F200" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G200" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H200" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F200" s="10"/>
+      <c r="G200" s="10"/>
+      <c r="H200" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="I200" s="10"/>
     </row>
     <row r="201" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
@@ -8242,25 +8434,25 @@
       <c r="B201" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="C201" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="D201" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E201" s="1" t="s">
+      <c r="E201" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F201" s="1" t="s">
+      <c r="F201" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G201" s="1" t="s">
+      <c r="G201" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H201" s="1" t="s">
+      <c r="H201" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I201" s="1" t="s">
+      <c r="I201" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8271,27 +8463,17 @@
       <c r="B202" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C202" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D202" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E202" s="4" t="s">
+      <c r="C202" s="10"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F202" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G202" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="I202" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F202" s="10"/>
+      <c r="G202" s="10"/>
+      <c r="H202" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="I202" s="10"/>
     </row>
     <row r="203" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
@@ -8300,25 +8482,25 @@
       <c r="B203" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="C203" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D203" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E203" s="1" t="s">
+      <c r="E203" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F203" s="1" t="s">
+      <c r="F203" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G203" s="1" t="s">
+      <c r="G203" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H203" s="1" t="s">
+      <c r="H203" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I203" s="1" t="s">
+      <c r="I203" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8329,27 +8511,17 @@
       <c r="B204" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C204" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E204" s="4" t="s">
+      <c r="C204" s="10"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F204" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G204" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H204" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="I204" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F204" s="10"/>
+      <c r="G204" s="10"/>
+      <c r="H204" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="I204" s="10"/>
     </row>
     <row r="205" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
@@ -8358,25 +8530,25 @@
       <c r="B205" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="C205" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D205" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E205" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="F205" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G205" s="1" t="s">
+      <c r="G205" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H205" s="1" t="s">
+      <c r="H205" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I205" s="1" t="s">
+      <c r="I205" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8387,27 +8559,17 @@
       <c r="B206" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C206" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E206" s="4" t="s">
+      <c r="C206" s="10"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F206" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G206" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H206" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="I206" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F206" s="10"/>
+      <c r="G206" s="10"/>
+      <c r="H206" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="I206" s="10"/>
     </row>
     <row r="207" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
@@ -8416,25 +8578,25 @@
       <c r="B207" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="C207" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="D207" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E207" s="1" t="s">
+      <c r="E207" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F207" s="1" t="s">
+      <c r="F207" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G207" s="1" t="s">
+      <c r="G207" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H207" s="1" t="s">
+      <c r="H207" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I207" s="1" t="s">
+      <c r="I207" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8445,27 +8607,17 @@
       <c r="B208" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C208" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D208" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E208" s="4" t="s">
+      <c r="C208" s="10"/>
+      <c r="D208" s="10"/>
+      <c r="E208" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F208" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G208" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H208" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="I208" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F208" s="10"/>
+      <c r="G208" s="10"/>
+      <c r="H208" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="I208" s="10"/>
     </row>
     <row r="209" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
@@ -8474,25 +8626,25 @@
       <c r="B209" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="C209" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D209" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E209" s="1" t="s">
+      <c r="E209" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F209" s="1" t="s">
+      <c r="F209" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G209" s="1" t="s">
+      <c r="G209" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H209" s="1" t="s">
+      <c r="H209" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I209" s="1" t="s">
+      <c r="I209" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8503,27 +8655,17 @@
       <c r="B210" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C210" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E210" s="4" t="s">
+      <c r="C210" s="10"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F210" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G210" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H210" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="I210" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F210" s="10"/>
+      <c r="G210" s="10"/>
+      <c r="H210" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="I210" s="10"/>
     </row>
     <row r="211" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
@@ -8532,25 +8674,25 @@
       <c r="B211" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="C211" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D211" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E211" s="1" t="s">
+      <c r="E211" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F211" s="1" t="s">
+      <c r="F211" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G211" s="1" t="s">
+      <c r="G211" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H211" s="1" t="s">
+      <c r="H211" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I211" s="1" t="s">
+      <c r="I211" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8561,27 +8703,17 @@
       <c r="B212" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C212" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E212" s="4" t="s">
+      <c r="C212" s="10"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F212" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G212" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H212" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="I212" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F212" s="10"/>
+      <c r="G212" s="10"/>
+      <c r="H212" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="I212" s="10"/>
     </row>
     <row r="213" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
@@ -8590,25 +8722,25 @@
       <c r="B213" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="C213" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D213" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E213" s="1" t="s">
+      <c r="E213" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F213" s="1" t="s">
+      <c r="F213" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G213" s="1" t="s">
+      <c r="G213" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H213" s="1" t="s">
+      <c r="H213" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I213" s="1" t="s">
+      <c r="I213" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8619,27 +8751,17 @@
       <c r="B214" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E214" s="4" t="s">
+      <c r="C214" s="10"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F214" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G214" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="I214" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F214" s="10"/>
+      <c r="G214" s="10"/>
+      <c r="H214" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="I214" s="10"/>
     </row>
     <row r="215" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
@@ -8648,25 +8770,25 @@
       <c r="B215" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="C215" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E215" s="1" t="s">
+      <c r="E215" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F215" s="1" t="s">
+      <c r="F215" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G215" s="1" t="s">
+      <c r="G215" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H215" s="1" t="s">
+      <c r="H215" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I215" s="1" t="s">
+      <c r="I215" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8677,27 +8799,17 @@
       <c r="B216" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C216" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E216" s="4" t="s">
+      <c r="C216" s="10"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F216" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H216" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F216" s="10"/>
+      <c r="G216" s="10"/>
+      <c r="H216" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="I216" s="10"/>
     </row>
     <row r="217" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
@@ -8706,25 +8818,25 @@
       <c r="B217" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="C217" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D217" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E217" s="1" t="s">
+      <c r="E217" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="F217" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G217" s="1" t="s">
+      <c r="G217" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H217" s="1" t="s">
+      <c r="H217" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I217" s="1" t="s">
+      <c r="I217" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8735,27 +8847,17 @@
       <c r="B218" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C218" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E218" s="4" t="s">
+      <c r="C218" s="10"/>
+      <c r="D218" s="10"/>
+      <c r="E218" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F218" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G218" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H218" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="I218" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F218" s="10"/>
+      <c r="G218" s="10"/>
+      <c r="H218" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="I218" s="10"/>
     </row>
     <row r="219" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
@@ -8764,25 +8866,25 @@
       <c r="B219" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="C219" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E219" s="1" t="s">
+      <c r="E219" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F219" s="1" t="s">
+      <c r="F219" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G219" s="1" t="s">
+      <c r="G219" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H219" s="1" t="s">
+      <c r="H219" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I219" s="1" t="s">
+      <c r="I219" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8793,27 +8895,17 @@
       <c r="B220" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C220" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E220" s="4" t="s">
+      <c r="C220" s="10"/>
+      <c r="D220" s="10"/>
+      <c r="E220" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F220" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G220" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H220" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="I220" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F220" s="10"/>
+      <c r="G220" s="10"/>
+      <c r="H220" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="I220" s="10"/>
     </row>
     <row r="221" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
@@ -8822,25 +8914,25 @@
       <c r="B221" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="C221" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="D221" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E221" s="1" t="s">
+      <c r="E221" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F221" s="1" t="s">
+      <c r="F221" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G221" s="1" t="s">
+      <c r="G221" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H221" s="1" t="s">
+      <c r="H221" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I221" s="1" t="s">
+      <c r="I221" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8851,27 +8943,17 @@
       <c r="B222" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C222" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E222" s="4" t="s">
+      <c r="C222" s="10"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F222" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G222" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H222" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="I222" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F222" s="10"/>
+      <c r="G222" s="10"/>
+      <c r="H222" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="I222" s="10"/>
     </row>
     <row r="223" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
@@ -8880,25 +8962,25 @@
       <c r="B223" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="C223" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="D223" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E223" s="1" t="s">
+      <c r="E223" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F223" s="1" t="s">
+      <c r="F223" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G223" s="1" t="s">
+      <c r="G223" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H223" s="1" t="s">
+      <c r="H223" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I223" s="1" t="s">
+      <c r="I223" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8909,27 +8991,17 @@
       <c r="B224" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C224" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E224" s="4" t="s">
+      <c r="C224" s="10"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F224" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G224" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H224" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="I224" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F224" s="10"/>
+      <c r="G224" s="10"/>
+      <c r="H224" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="I224" s="10"/>
     </row>
     <row r="225" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
@@ -8938,25 +9010,25 @@
       <c r="B225" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="C225" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="D225" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E225" s="1" t="s">
+      <c r="E225" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F225" s="1" t="s">
+      <c r="F225" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G225" s="1" t="s">
+      <c r="G225" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H225" s="1" t="s">
+      <c r="H225" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I225" s="1" t="s">
+      <c r="I225" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8967,27 +9039,17 @@
       <c r="B226" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C226" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E226" s="4" t="s">
+      <c r="C226" s="10"/>
+      <c r="D226" s="10"/>
+      <c r="E226" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F226" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H226" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="I226" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F226" s="10"/>
+      <c r="G226" s="10"/>
+      <c r="H226" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="I226" s="10"/>
     </row>
     <row r="227" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
@@ -8996,25 +9058,25 @@
       <c r="B227" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="C227" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E227" s="1" t="s">
+      <c r="E227" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F227" s="1" t="s">
+      <c r="F227" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G227" s="1" t="s">
+      <c r="G227" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H227" s="1" t="s">
+      <c r="H227" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I227" s="1" t="s">
+      <c r="I227" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9025,27 +9087,17 @@
       <c r="B228" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C228" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E228" s="4" t="s">
+      <c r="C228" s="10"/>
+      <c r="D228" s="10"/>
+      <c r="E228" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F228" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G228" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H228" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="I228" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F228" s="10"/>
+      <c r="G228" s="10"/>
+      <c r="H228" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="I228" s="10"/>
     </row>
     <row r="229" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
@@ -9054,25 +9106,25 @@
       <c r="B229" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C229" s="1" t="s">
+      <c r="C229" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E229" s="1" t="s">
+      <c r="E229" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F229" s="1" t="s">
+      <c r="F229" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G229" s="1" t="s">
+      <c r="G229" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H229" s="1" t="s">
+      <c r="H229" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I229" s="1" t="s">
+      <c r="I229" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9083,112 +9135,117 @@
       <c r="B230" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C230" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D230" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E230" s="4" t="s">
+      <c r="C230" s="10"/>
+      <c r="D230" s="10"/>
+      <c r="E230" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F230" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G230" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H230" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="I230" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="F230" s="10"/>
+      <c r="G230" s="10"/>
+      <c r="H230" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="I230" s="10"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C231" s="6"/>
+      <c r="D231" s="6"/>
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
+      <c r="G231" s="6"/>
+      <c r="H231" s="6"/>
+      <c r="I231" s="6"/>
     </row>
     <row r="232" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C232" s="6"/>
+      <c r="D232" s="6"/>
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
+      <c r="G232" s="6"/>
+      <c r="H232" s="6"/>
+      <c r="I232" s="6"/>
     </row>
     <row r="233" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B233" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="D233" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E233" s="2" t="s">
+      <c r="E233" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F233" s="2" t="s">
+      <c r="F233" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G233" s="2" t="s">
+      <c r="G233" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="H233" s="6"/>
+      <c r="I233" s="6"/>
     </row>
     <row r="234" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B234" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C234" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D234" s="5" t="s">
+      <c r="C234" s="10"/>
+      <c r="D234" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="E234" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="G234" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="G234" s="12"/>
+      <c r="H234" s="6"/>
+      <c r="I234" s="6"/>
     </row>
     <row r="235" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B235" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C235" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D235" s="5" t="s">
+      <c r="C235" s="10"/>
+      <c r="D235" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="E235" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="G235" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="G235" s="12"/>
+      <c r="H235" s="6"/>
+      <c r="I235" s="6"/>
     </row>
     <row r="236" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B236" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C236" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D236" s="5" t="s">
+      <c r="C236" s="10"/>
+      <c r="D236" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E236" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="G236" s="5" t="s">
-        <v>542</v>
-      </c>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="G236" s="12"/>
+      <c r="H236" s="6"/>
+      <c r="I236" s="6"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C237" s="6"/>
+      <c r="D237" s="6"/>
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
+      <c r="G237" s="6"/>
+      <c r="H237" s="6"/>
+      <c r="I237" s="6"/>
     </row>
     <row r="238" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
@@ -9197,25 +9254,25 @@
       <c r="B238" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="C238" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="D238" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E238" s="1" t="s">
+      <c r="E238" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F238" s="1" t="s">
+      <c r="F238" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G238" s="1" t="s">
+      <c r="G238" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H238" s="1" t="s">
+      <c r="H238" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I238" s="1" t="s">
+      <c r="I238" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9226,72 +9283,84 @@
       <c r="B239" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C239" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D239" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E239" s="4" t="s">
+      <c r="C239" s="10"/>
+      <c r="D239" s="10"/>
+      <c r="E239" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F239" s="4" t="s">
+      <c r="F239" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="G239" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H239" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="I239" s="4" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="241" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G239" s="10"/>
+      <c r="H239" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="I239" s="10"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C240" s="6"/>
+      <c r="D240" s="6"/>
+      <c r="E240" s="6"/>
+      <c r="F240" s="6"/>
+      <c r="G240" s="6"/>
+      <c r="H240" s="6"/>
+      <c r="I240" s="6"/>
+    </row>
+    <row r="241" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="242" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+      <c r="C241" s="6"/>
+      <c r="D241" s="6"/>
+      <c r="E241" s="6"/>
+      <c r="F241" s="6"/>
+      <c r="G241" s="6"/>
+      <c r="H241" s="6"/>
+      <c r="I241" s="6"/>
+    </row>
+    <row r="242" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D242" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E242" s="2" t="s">
+      <c r="E242" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F242" s="2" t="s">
+      <c r="F242" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="243" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H242" s="6"/>
+      <c r="I242" s="6"/>
+    </row>
+    <row r="243" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B243" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="D243" s="5" t="s">
+      <c r="D243" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="E243" s="5" t="s">
+      <c r="E243" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="F243" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>715</v>
-      </c>
+      <c r="F243" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="G243" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="H243" s="6"/>
+      <c r="I243" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
